--- a/contractor_forms/026_web_application_development_agreement--contractor_forms.xlsx
+++ b/contractor_forms/026_web_application_development_agreement--contractor_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'PayPal', 'value': 'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'bank_transfer',_'value':_'bank_transfer'}</t>
+          <t>bank_transfer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Bank Transfer', 'value': 'bank_transfer'}</t>
+          <t>bank transfer</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'credit_card',_'value':_'credit_card'}</t>
+          <t>credit_card</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Credit Card', 'value': 'credit_card'}</t>
+          <t>credit card</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'yes',_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Yes', 'value': 'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'no',_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'No', 'value': 'no'}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'yes',_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Yes', 'value': 'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'no',_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'No', 'value': 'no'}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'yes',_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Yes', 'value': 'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'no',_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'No', 'value': 'no'}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -1296,12 +1296,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'yes',_'value':_'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Yes', 'value': 'yes'}</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'no',_'value':_'no'}</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'No', 'value': 'no'}</t>
+          <t>no</t>
         </is>
       </c>
     </row>
